--- a/generation_zy/hiwo-任务2-1.xlsx
+++ b/generation_zy/hiwo-任务2-1.xlsx
@@ -1785,12 +1785,10 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>B01-FY96</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>40</v>
-      </c>
+          <t>FY96-B01</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
       <c r="F3" s="1" t="inlineStr">
         <is>
           <t>℃</t>
@@ -1801,41 +1799,27 @@
           <t>等待</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>关盖</t>
-        </is>
-      </c>
+      <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="J3" s="2" t="n"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
           <t>分钟</t>
         </is>
       </c>
-      <c r="L3" s="2" t="n">
-        <v>900</v>
-      </c>
+      <c r="L3" s="2" t="n"/>
       <c r="M3" s="1" t="inlineStr">
         <is>
           <t>RPM</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="N3" s="2" t="n"/>
       <c r="O3" s="1" t="inlineStr">
         <is>
           <t>分钟</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>开盖</t>
-        </is>
-      </c>
+      <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n">
         <v>5</v>
       </c>
@@ -1884,9 +1868,7 @@
           <t>微升</t>
         </is>
       </c>
-      <c r="AC3" s="2" t="n">
-        <v>3</v>
-      </c>
+      <c r="AC3" s="2" t="n"/>
       <c r="AD3" s="1" t="inlineStr">
         <is>
           <t>分钟</t>
@@ -2105,7 +2087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="10"/>
@@ -2161,6 +2143,267 @@
         <is>
           <t>金属板编号</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SS-A03</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B01-FY96</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SS-A03</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B01-FY96</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>300</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SS-A03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B01-FY96</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>300</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SS-A03</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B01-FY96</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>300</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SS-A03</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>B01-FY96</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>300</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SS-A03</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B01-FY96</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>300</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SS-A03</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>B01-FY96</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>300</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SS-A03</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>11</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B01-FY96</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>300</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SS-A03</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>11</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B01-FY96</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>300</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2240,7 +2483,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -2251,88 +2494,248 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>190</v>
+        <v>400</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>A05</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SS-A03</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>B01-FY96</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SS-A03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>B01-FY96</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SS-A03</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>B01-FY96</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SS-A03</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>B01-FY96</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SS-A03</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>B01-FY96</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SS-A03</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>B01-FY96</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SS-A03</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>B01-FY96</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n"/>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SS-A03</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>B01-FY96</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -2432,33 +2835,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>B03-1</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>B01-FY96</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>190</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -2630,33 +3013,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>B03-1</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>B02-96</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>A05</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -2828,33 +3191,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>B03-1</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>2A01-GL96</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>190</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>3</v>
-      </c>
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -3026,62 +3369,22 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>B01-FY96</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>B02-96</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>B02-96</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>2A01-GL96</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
